--- a/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="28">
   <si>
     <t>每个方块的小方块数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -118,6 +118,18 @@
   </si>
   <si>
     <t>##column#var</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大行数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大列数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每行经验值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -183,12 +195,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -197,16 +224,16 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -489,52 +516,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="26.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="5">
@@ -542,13 +569,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="5">
@@ -556,13 +583,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="5">
@@ -570,13 +597,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="5">
@@ -584,13 +611,13 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="5">
@@ -598,13 +625,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="5">
@@ -612,13 +639,13 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="5">
@@ -626,13 +653,13 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="6">
@@ -640,13 +667,13 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="6">
@@ -654,13 +681,13 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="6">
@@ -668,13 +695,13 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="6">
@@ -682,13 +709,13 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="6">
@@ -696,13 +723,13 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="6">
@@ -710,13 +737,13 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="6">
@@ -724,13 +751,13 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="6">
@@ -739,13 +766,13 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="6">
@@ -754,13 +781,13 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="6">
@@ -768,17 +795,60 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="6">
         <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75">
+      <c r="A22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75">
+      <c r="A23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75">
+      <c r="A24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="6">
+        <f>D5*D23</f>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
   <si>
     <t>每个方块的小方块数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -130,6 +130,38 @@
   </si>
   <si>
     <t>每行经验值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色成长倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色强度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色强度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色强度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色成长倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色成长倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿色角色1级战力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -137,7 +169,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +207,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -222,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -235,6 +275,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="2" customWidth="1"/>
@@ -851,6 +897,104 @@
         <v>100</v>
       </c>
     </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="6">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="6">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="8">
+        <v>265</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="38">
   <si>
     <t>每个方块的小方块数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,6 +162,14 @@
   </si>
   <si>
     <t>绿色角色1级战力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均肉鸽技能倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -562,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="2" customWidth="1"/>
@@ -995,6 +1003,20 @@
         <v>265</v>
       </c>
     </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1.0437000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
@@ -958,7 +958,7 @@
         <v>28</v>
       </c>
       <c r="D28" s="6">
-        <v>1.1200000000000001</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -972,7 +972,7 @@
         <v>32</v>
       </c>
       <c r="D29" s="6">
-        <v>1.1200000000000001</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -986,7 +986,7 @@
         <v>33</v>
       </c>
       <c r="D30" s="6">
-        <v>1.1200000000000001</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1000,7 +1000,7 @@
         <v>35</v>
       </c>
       <c r="D31" s="8">
-        <v>265</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:4">

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
@@ -1014,7 +1014,7 @@
         <v>36</v>
       </c>
       <c r="D32" s="6">
-        <v>1.0437000000000001</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
@@ -570,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="2" customWidth="1"/>
@@ -1017,8 +1017,14 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="6"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#游戏基本参数.xlsx
@@ -703,7 +703,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="5">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75">
@@ -717,7 +717,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="6">
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75">
@@ -731,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="6">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75">
@@ -759,7 +759,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75">
@@ -773,7 +773,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75">
@@ -787,7 +787,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
@@ -801,7 +801,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75">
@@ -816,7 +816,7 @@
       </c>
       <c r="D18" s="6">
         <f>SUM(D14:D16)/D7</f>
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
@@ -831,7 +831,7 @@
       </c>
       <c r="D19" s="6">
         <f>D18</f>
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75">
@@ -859,7 +859,7 @@
         <v>17</v>
       </c>
       <c r="D21" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75">
@@ -1000,7 +1000,7 @@
         <v>35</v>
       </c>
       <c r="D31" s="8">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:4">
